--- a/exports/trend_1d/AUROPHARMA_full_report.xlsx
+++ b/exports/trend_1d/AUROPHARMA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42039</v>
+        <v>42040</v>
       </c>
       <c r="H2" t="n">
-        <v>604.9</v>
+        <v>575.42</v>
       </c>
       <c r="I2" t="n">
         <v>580.9753853286079</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>6.86</v>
+        <v>1.66</v>
       </c>
       <c r="L2" t="n">
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.91</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>3.16</v>
+        <v>4.87</v>
       </c>
       <c r="O2" t="n">
         <v>-1.08</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42076</v>
+        <v>42079</v>
       </c>
       <c r="H3" t="n">
-        <v>574.15</v>
+        <v>597.92</v>
       </c>
       <c r="I3" t="n">
         <v>579.8949889870789</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K3" t="n">
-        <v>0.22</v>
+        <v>-3.91</v>
       </c>
       <c r="L3" t="n">
-        <v>4.08</v>
+        <v>4.26</v>
       </c>
       <c r="M3" t="n">
         <v>5.02</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.56</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>644.58</v>
+        <v>607.7</v>
       </c>
       <c r="I4" t="n">
         <v>614.5470912640703</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>1.64</v>
       </c>
       <c r="L4" t="n">
         <v>6.93</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>16.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42178</v>
+        <v>42179</v>
       </c>
       <c r="H5" t="n">
-        <v>697.98</v>
+        <v>721.63</v>
       </c>
       <c r="I5" t="n">
         <v>707.2606745250762</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K5" t="n">
-        <v>-14.86</v>
+        <v>-18.75</v>
       </c>
       <c r="L5" t="n">
-        <v>16.18</v>
+        <v>20.36</v>
       </c>
       <c r="M5" t="n">
         <v>2.05</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>804.45</v>
+        <v>713.8</v>
       </c>
       <c r="I6" t="n">
         <v>722.7844007199137</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K6" t="n">
-        <v>11.48</v>
+        <v>-1.09</v>
       </c>
       <c r="L6" t="n">
         <v>5.67</v>
@@ -783,7 +854,7 @@
         <v>4.58</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>11.27</v>
       </c>
       <c r="O6" t="n">
         <v>3.39</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>21.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42290</v>
+        <v>42291</v>
       </c>
       <c r="H7" t="n">
-        <v>780.95</v>
+        <v>805.95</v>
       </c>
       <c r="I7" t="n">
         <v>792.1024264703517</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.41</v>
+        <v>-12.91</v>
       </c>
       <c r="L7" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="M7" t="n">
         <v>2.43</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H8" t="n">
-        <v>797.9</v>
+        <v>786.75</v>
       </c>
       <c r="I8" t="n">
         <v>787.0811413260758</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>-1</v>
+        <v>-2.38</v>
       </c>
       <c r="L8" t="n">
         <v>3.22</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.63</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42360</v>
+        <v>42361</v>
       </c>
       <c r="H9" t="n">
-        <v>840.6</v>
+        <v>869.1</v>
       </c>
       <c r="I9" t="n">
         <v>846.7746009185609</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.84</v>
+        <v>-10.47</v>
       </c>
       <c r="L9" t="n">
-        <v>7.82</v>
+        <v>10.71</v>
       </c>
       <c r="M9" t="n">
         <v>1.68</v>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>3.39</v>
       </c>
       <c r="O9" t="n">
         <v>-1.4</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.5</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H10" t="n">
-        <v>840.75</v>
+        <v>829.3</v>
       </c>
       <c r="I10" t="n">
         <v>829.9928327138902</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.26</v>
+        <v>-4.58</v>
       </c>
       <c r="L10" t="n">
-        <v>5.07</v>
+        <v>8.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H11" t="n">
-        <v>705.45</v>
+        <v>718</v>
       </c>
       <c r="I11" t="n">
         <v>713.4855117361378</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>14.93</v>
+        <v>13.42</v>
       </c>
       <c r="L11" t="n">
         <v>2.18</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>15.1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42513</v>
+        <v>42514</v>
       </c>
       <c r="H12" t="n">
-        <v>759.7</v>
+        <v>727.8</v>
       </c>
       <c r="I12" t="n">
         <v>757.3304580211421</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K12" t="n">
-        <v>5.81</v>
+        <v>1.36</v>
       </c>
       <c r="L12" t="n">
         <v>3.13</v>
@@ -1125,7 +1268,7 @@
         <v>1.76</v>
       </c>
       <c r="N12" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42555</v>
+        <v>42556</v>
       </c>
       <c r="H13" t="n">
-        <v>757.8</v>
+        <v>771</v>
       </c>
       <c r="I13" t="n">
         <v>758.6293927290066</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.12</v>
+        <v>-5.94</v>
       </c>
       <c r="L13" t="n">
         <v>10.29</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.18</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42594</v>
+        <v>42598</v>
       </c>
       <c r="H14" t="n">
-        <v>747.45</v>
+        <v>733.95</v>
       </c>
       <c r="I14" t="n">
         <v>740.1112942942136</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.05</v>
+        <v>-4.81</v>
       </c>
       <c r="L14" t="n">
-        <v>4.53</v>
+        <v>5.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H15" t="n">
-        <v>783.25</v>
+        <v>807.2</v>
       </c>
       <c r="I15" t="n">
         <v>804.6660326773383</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.72</v>
+        <v>-9.98</v>
       </c>
       <c r="L15" t="n">
-        <v>9.68</v>
+        <v>10.35</v>
       </c>
       <c r="M15" t="n">
         <v>3.08</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.44</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H16" t="n">
-        <v>824.9</v>
+        <v>805.7</v>
       </c>
       <c r="I16" t="n">
         <v>807.5268060015272</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K16" t="n">
-        <v>2.19</v>
+        <v>-0.19</v>
       </c>
       <c r="L16" t="n">
         <v>3.77</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.85</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H17" t="n">
-        <v>694.55</v>
+        <v>699.65</v>
       </c>
       <c r="I17" t="n">
         <v>698.9911030820821</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K17" t="n">
-        <v>13.8</v>
+        <v>13.16</v>
       </c>
       <c r="L17" t="n">
         <v>2.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42776</v>
+        <v>42779</v>
       </c>
       <c r="H18" t="n">
-        <v>679.3</v>
+        <v>661.95</v>
       </c>
       <c r="I18" t="n">
         <v>664.5588833098124</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.91</v>
+        <v>-5.39</v>
       </c>
       <c r="L18" t="n">
         <v>6.16</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.33</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42887</v>
+        <v>42888</v>
       </c>
       <c r="H19" t="n">
-        <v>579.65</v>
+        <v>593.4</v>
       </c>
       <c r="I19" t="n">
         <v>581.2283046950826</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K19" t="n">
-        <v>12.43</v>
+        <v>10.36</v>
       </c>
       <c r="L19" t="n">
         <v>7.31</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.52</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H20" t="n">
-        <v>726.3</v>
+        <v>683.6</v>
       </c>
       <c r="I20" t="n">
         <v>702.5634651325995</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K20" t="n">
-        <v>22.4</v>
+        <v>15.2</v>
       </c>
       <c r="L20" t="n">
         <v>3.06</v>
@@ -1581,7 +1820,7 @@
         <v>1.44</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>5.88</v>
       </c>
       <c r="O20" t="n">
         <v>2.37</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.66</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H21" t="n">
-        <v>745.5</v>
+        <v>757.75</v>
       </c>
       <c r="I21" t="n">
         <v>748.8193672946558</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.06</v>
+        <v>-10.85</v>
       </c>
       <c r="L21" t="n">
         <v>13.52</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.59</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43049</v>
+        <v>43052</v>
       </c>
       <c r="H22" t="n">
-        <v>740.1</v>
+        <v>710.2</v>
       </c>
       <c r="I22" t="n">
         <v>732.2064918942754</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.33</v>
+        <v>-6.28</v>
       </c>
       <c r="L22" t="n">
-        <v>4.32</v>
+        <v>6.76</v>
       </c>
       <c r="M22" t="n">
         <v>0.28</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.6</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H23" t="n">
-        <v>590.45</v>
+        <v>599.15</v>
       </c>
       <c r="I23" t="n">
         <v>595.9266799705456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K23" t="n">
-        <v>16.86</v>
+        <v>15.64</v>
       </c>
       <c r="L23" t="n">
         <v>5.6</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.93</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H24" t="n">
-        <v>594.9</v>
+        <v>579.4</v>
       </c>
       <c r="I24" t="n">
         <v>590.4770118880713</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.71</v>
+        <v>-3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.37</v>
       </c>
       <c r="N24" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
         <v>1.47</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43264</v>
+        <v>43265</v>
       </c>
       <c r="H25" t="n">
-        <v>584.9</v>
+        <v>609.45</v>
       </c>
       <c r="I25" t="n">
         <v>597.1595830986789</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.95</v>
+        <v>-5.19</v>
       </c>
       <c r="L25" t="n">
         <v>6.08</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>13.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43299</v>
+        <v>43300</v>
       </c>
       <c r="H26" t="n">
-        <v>576.3</v>
+        <v>567.85</v>
       </c>
       <c r="I26" t="n">
         <v>571.1780427316252</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.44</v>
+        <v>-6.83</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.29</v>
       </c>
       <c r="M26" t="n">
         <v>0.67</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43325</v>
+        <v>43326</v>
       </c>
       <c r="H27" t="n">
-        <v>618.8</v>
+        <v>631.35</v>
       </c>
       <c r="I27" t="n">
         <v>629.4097755246052</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.970000000000001</v>
+        <v>-11.18</v>
       </c>
       <c r="L27" t="n">
         <v>12.12</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.38</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H28" t="n">
-        <v>751.35</v>
+        <v>733.3</v>
       </c>
       <c r="I28" t="n">
         <v>744.4715389177529</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K28" t="n">
-        <v>19.01</v>
+        <v>16.15</v>
       </c>
       <c r="L28" t="n">
         <v>3.61</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.13</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43474</v>
+        <v>43475</v>
       </c>
       <c r="H29" t="n">
-        <v>757.25</v>
+        <v>776.95</v>
       </c>
       <c r="I29" t="n">
         <v>771.7595577376352</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.27</v>
+        <v>-5.95</v>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>6.23</v>
       </c>
       <c r="M29" t="n">
         <v>1.9</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.81</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H30" t="n">
-        <v>748.75</v>
+        <v>722.6</v>
       </c>
       <c r="I30" t="n">
         <v>736.9080305949154</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.63</v>
+        <v>-7</v>
       </c>
       <c r="L30" t="n">
-        <v>6.13</v>
+        <v>7.59</v>
       </c>
       <c r="M30" t="n">
         <v>0.74</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.76</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43537</v>
+        <v>43538</v>
       </c>
       <c r="H31" t="n">
-        <v>766.25</v>
+        <v>778.65</v>
       </c>
       <c r="I31" t="n">
         <v>775.9580114232385</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.04</v>
+        <v>-7.76</v>
       </c>
       <c r="L31" t="n">
-        <v>8.76</v>
+        <v>8.77</v>
       </c>
       <c r="M31" t="n">
         <v>1.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.17</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H32" t="n">
-        <v>765.2</v>
+        <v>756.65</v>
       </c>
       <c r="I32" t="n">
         <v>760.9912816767107</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.73</v>
+        <v>-2.83</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="M32" t="n">
         <v>0.58</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.91</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H33" t="n">
-        <v>599.15</v>
+        <v>613.05</v>
       </c>
       <c r="I33" t="n">
         <v>609.6313744261088</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K33" t="n">
-        <v>20.82</v>
+        <v>18.98</v>
       </c>
       <c r="L33" t="n">
         <v>1.37</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>9.44</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H34" t="n">
-        <v>597.2</v>
+        <v>589</v>
       </c>
       <c r="I34" t="n">
         <v>589.6224604970242</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.59</v>
+        <v>-3.92</v>
       </c>
       <c r="L34" t="n">
-        <v>3.94</v>
+        <v>5.39</v>
       </c>
       <c r="M34" t="n">
         <v>2.78</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43818</v>
+        <v>43819</v>
       </c>
       <c r="H35" t="n">
-        <v>464.2</v>
+        <v>470.4</v>
       </c>
       <c r="I35" t="n">
         <v>469.5188436152841</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K35" t="n">
-        <v>21.19</v>
+        <v>20.14</v>
       </c>
       <c r="L35" t="n">
         <v>1.7</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H36" t="n">
-        <v>599.75</v>
+        <v>504</v>
       </c>
       <c r="I36" t="n">
         <v>517.8597792169984</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K36" t="n">
-        <v>27.5</v>
+        <v>7.14</v>
       </c>
       <c r="L36" t="n">
         <v>6.04</v>
       </c>
       <c r="M36" t="n">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>5.34</v>
+        <v>15.96</v>
       </c>
       <c r="O36" t="n">
         <v>1.34</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>24.04</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H37" t="n">
-        <v>382.4</v>
+        <v>445.7</v>
       </c>
       <c r="I37" t="n">
         <v>444.7428168190435</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K37" t="n">
-        <v>24.13</v>
+        <v>11.57</v>
       </c>
       <c r="L37" t="n">
         <v>7.1</v>
@@ -2550,7 +2993,7 @@
         <v>8.59</v>
       </c>
       <c r="N37" t="n">
-        <v>10.87</v>
+        <v>16.55</v>
       </c>
       <c r="O37" t="n">
         <v>-15.96</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>35.35</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H38" t="n">
-        <v>868.9</v>
+        <v>808.9</v>
       </c>
       <c r="I38" t="n">
         <v>847.6575480500499</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K38" t="n">
-        <v>94.95</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>11.72</v>
@@ -2607,7 +3062,7 @@
         <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>5.66</v>
+        <v>6.91</v>
       </c>
       <c r="O38" t="n">
         <v>16.55</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44147</v>
+        <v>44148</v>
       </c>
       <c r="H39" t="n">
-        <v>839</v>
+        <v>858.1</v>
       </c>
       <c r="I39" t="n">
         <v>842.9327953417604</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.72</v>
+        <v>-6.08</v>
       </c>
       <c r="L39" t="n">
         <v>8.59</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.07</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H40" t="n">
-        <v>888.55</v>
+        <v>856.4</v>
       </c>
       <c r="I40" t="n">
         <v>885.1629635132367</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K40" t="n">
-        <v>3.55</v>
+        <v>-0.2</v>
       </c>
       <c r="L40" t="n">
         <v>6.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.43</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44291</v>
+        <v>44292</v>
       </c>
       <c r="H41" t="n">
-        <v>882.2</v>
+        <v>892.8</v>
       </c>
       <c r="I41" t="n">
         <v>890.4953586627537</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.01</v>
+        <v>-4.25</v>
       </c>
       <c r="L41" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="M41" t="n">
         <v>1.42</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44369</v>
+        <v>44370</v>
       </c>
       <c r="H42" t="n">
-        <v>952.6</v>
+        <v>944.4</v>
       </c>
       <c r="I42" t="n">
         <v>949.0590570468593</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K42" t="n">
-        <v>6.7</v>
+        <v>5.78</v>
       </c>
       <c r="L42" t="n">
         <v>1.6</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.4</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44537</v>
+        <v>44538</v>
       </c>
       <c r="H43" t="n">
-        <v>673.35</v>
+        <v>701.95</v>
       </c>
       <c r="I43" t="n">
         <v>695.0506687339407</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K43" t="n">
-        <v>28.7</v>
+        <v>25.67</v>
       </c>
       <c r="L43" t="n">
         <v>7.26</v>
@@ -2892,7 +3407,7 @@
         <v>4.57</v>
       </c>
       <c r="N43" t="n">
-        <v>3.72</v>
+        <v>4.25</v>
       </c>
       <c r="O43" t="n">
         <v>-0.86</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>7</v>
+      </c>
+      <c r="U43" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.04</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H44" t="n">
-        <v>685.8</v>
+        <v>668.8</v>
       </c>
       <c r="I44" t="n">
         <v>680.1900766078791</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.3</v>
+        <v>-4.72</v>
       </c>
       <c r="L44" t="n">
         <v>5.33</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.61</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44601</v>
+        <v>44602</v>
       </c>
       <c r="H45" t="n">
-        <v>656.05</v>
+        <v>684.4</v>
       </c>
       <c r="I45" t="n">
         <v>677.1091306381043</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>1.91</v>
+        <v>-2.33</v>
       </c>
       <c r="L45" t="n">
         <v>3.92</v>
@@ -3006,7 +3545,7 @@
         <v>1.71</v>
       </c>
       <c r="N45" t="n">
-        <v>3.63</v>
+        <v>4.32</v>
       </c>
       <c r="O45" t="n">
         <v>-2.48</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.64</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H46" t="n">
-        <v>637.05</v>
+        <v>605.45</v>
       </c>
       <c r="I46" t="n">
         <v>620.956141868232</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.92</v>
+        <v>-11.54</v>
       </c>
       <c r="L46" t="n">
-        <v>10.13</v>
+        <v>12.17</v>
       </c>
       <c r="M46" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>4.96</v>
       </c>
       <c r="O46" t="n">
         <v>4.32</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.98</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44637</v>
+        <v>44641</v>
       </c>
       <c r="H47" t="n">
-        <v>640.35</v>
+        <v>679.4</v>
       </c>
       <c r="I47" t="n">
         <v>662.7071416070775</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.76</v>
+        <v>-12.21</v>
       </c>
       <c r="L47" t="n">
-        <v>8.18</v>
+        <v>13.8</v>
       </c>
       <c r="M47" t="n">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="N47" t="n">
-        <v>3.24</v>
+        <v>6.1</v>
       </c>
       <c r="O47" t="n">
         <v>-4.96</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.97</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H48" t="n">
-        <v>666.7</v>
+        <v>638.9</v>
       </c>
       <c r="I48" t="n">
         <v>647.9657118142622</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.87</v>
+        <v>-5.96</v>
       </c>
       <c r="L48" t="n">
-        <v>4.65</v>
+        <v>6.54</v>
       </c>
       <c r="M48" t="n">
         <v>1.43</v>
       </c>
       <c r="N48" t="n">
-        <v>2.5</v>
+        <v>4.17</v>
       </c>
       <c r="O48" t="n">
         <v>6.1</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.99</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H49" t="n">
-        <v>558.15</v>
+        <v>575.2</v>
       </c>
       <c r="I49" t="n">
         <v>564.8907110921266</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K49" t="n">
-        <v>12.64</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L49" t="n">
         <v>4.34</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.53</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44805</v>
+        <v>44806</v>
       </c>
       <c r="H50" t="n">
-        <v>539.05</v>
+        <v>534.9</v>
       </c>
       <c r="I50" t="n">
         <v>538.2689170564319</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.28</v>
+        <v>-7.01</v>
       </c>
       <c r="L50" t="n">
         <v>7.46</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H51" t="n">
-        <v>535.2</v>
+        <v>544.25</v>
       </c>
       <c r="I51" t="n">
         <v>541.638314848295</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.06</v>
+        <v>-1.75</v>
       </c>
       <c r="L51" t="n">
         <v>4.08</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.74</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H52" t="n">
-        <v>541.4</v>
+        <v>477.8</v>
       </c>
       <c r="I52" t="n">
         <v>518.5342518653906</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.52</v>
+        <v>-12.21</v>
       </c>
       <c r="L52" t="n">
-        <v>7.09</v>
+        <v>14.71</v>
       </c>
       <c r="M52" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>4.69</v>
+        <v>11.75</v>
       </c>
       <c r="O52" t="n">
         <v>1.69</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>17.76</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H53" t="n">
-        <v>418.65</v>
+        <v>445.05</v>
       </c>
       <c r="I53" t="n">
         <v>437.6062615994913</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K53" t="n">
-        <v>12.38</v>
+        <v>6.85</v>
       </c>
       <c r="L53" t="n">
         <v>12.85</v>
@@ -3462,7 +4097,7 @@
         <v>1.51</v>
       </c>
       <c r="N53" t="n">
-        <v>3.46</v>
+        <v>6.31</v>
       </c>
       <c r="O53" t="n">
         <v>-11.75</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H54" t="n">
-        <v>1066.75</v>
+        <v>1018.25</v>
       </c>
       <c r="I54" t="n">
         <v>1050.329828209305</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K54" t="n">
-        <v>139.69</v>
+        <v>128.79</v>
       </c>
       <c r="L54" t="n">
         <v>6.64</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>13</v>
+      </c>
+      <c r="U54" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>15.72</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H55" t="n">
-        <v>1088.75</v>
+        <v>1113.35</v>
       </c>
       <c r="I55" t="n">
         <v>1109.444623335749</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.92</v>
+        <v>-9.34</v>
       </c>
       <c r="L55" t="n">
-        <v>9.4</v>
+        <v>11.13</v>
       </c>
       <c r="M55" t="n">
         <v>3.26</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="H56" t="n">
-        <v>1511.35</v>
+        <v>1460.7</v>
       </c>
       <c r="I56" t="n">
         <v>1463.393438543024</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K56" t="n">
-        <v>35.75</v>
+        <v>31.2</v>
       </c>
       <c r="L56" t="n">
         <v>3.96</v>
@@ -3633,7 +4304,7 @@
         <v>2.26</v>
       </c>
       <c r="N56" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
         <v>2.26</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H57" t="n">
-        <v>1269.95</v>
+        <v>1298.3</v>
       </c>
       <c r="I57" t="n">
         <v>1282.799856349543</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K57" t="n">
-        <v>13.06</v>
+        <v>11.12</v>
       </c>
       <c r="L57" t="n">
         <v>4.06</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H58" t="n">
-        <v>1281.65</v>
+        <v>1248.4</v>
       </c>
       <c r="I58" t="n">
         <v>1249.150360619424</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.28</v>
+        <v>-3.84</v>
       </c>
       <c r="L58" t="n">
-        <v>2.79</v>
+        <v>4.11</v>
       </c>
       <c r="M58" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="N58" t="n">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="O58" t="n">
         <v>2.23</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.09</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H59" t="n">
-        <v>1163.8</v>
+        <v>1174.15</v>
       </c>
       <c r="I59" t="n">
         <v>1166.601735141631</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K59" t="n">
-        <v>6.78</v>
+        <v>5.95</v>
       </c>
       <c r="L59" t="n">
         <v>3.72</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>8.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H60" t="n">
-        <v>1176.35</v>
+        <v>1105.35</v>
       </c>
       <c r="I60" t="n">
         <v>1122.075697244346</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>0.19</v>
+        <v>-5.86</v>
       </c>
       <c r="L60" t="n">
-        <v>4.83</v>
+        <v>10.57</v>
       </c>
       <c r="M60" t="n">
         <v>0.64</v>
       </c>
       <c r="N60" t="n">
-        <v>3.14</v>
+        <v>6.04</v>
       </c>
       <c r="O60" t="n">
         <v>0.89</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>15.49</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H61" t="n">
-        <v>1187.7</v>
+        <v>1246.8</v>
       </c>
       <c r="I61" t="n">
         <v>1228.181730862191</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.45</v>
+        <v>-12.8</v>
       </c>
       <c r="L61" t="n">
-        <v>9.960000000000001</v>
+        <v>13.36</v>
       </c>
       <c r="M61" t="n">
         <v>3.92</v>
       </c>
       <c r="N61" t="n">
-        <v>4.83</v>
+        <v>4.98</v>
       </c>
       <c r="O61" t="n">
         <v>-6.04</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.63</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H62" t="n">
-        <v>1109.7</v>
+        <v>1105.3</v>
       </c>
       <c r="I62" t="n">
         <v>1109.443275265282</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K62" t="n">
-        <v>-11</v>
+        <v>-11.35</v>
       </c>
       <c r="L62" t="n">
         <v>12.22</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>8.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="H63" t="n">
-        <v>1156.1</v>
+        <v>1191.3</v>
       </c>
       <c r="I63" t="n">
         <v>1179.478637983395</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.6</v>
+        <v>-7.78</v>
       </c>
       <c r="L63" t="n">
-        <v>5.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M63" t="n">
         <v>2.59</v>
       </c>
       <c r="N63" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="O63" t="n">
         <v>-0.4</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H64" t="n">
-        <v>1138.5</v>
+        <v>1101.4</v>
       </c>
       <c r="I64" t="n">
         <v>1103.448187307683</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.43</v>
+        <v>-7.55</v>
       </c>
       <c r="L64" t="n">
-        <v>6.39</v>
+        <v>7.66</v>
       </c>
       <c r="M64" t="n">
         <v>1.35</v>
       </c>
       <c r="N64" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="O64" t="n">
         <v>3.04</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.77</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H65" t="n">
-        <v>1050.3</v>
+        <v>1109.2</v>
       </c>
       <c r="I65" t="n">
         <v>1100.70659019108</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K65" t="n">
-        <v>4.64</v>
+        <v>-0.71</v>
       </c>
       <c r="L65" t="n">
         <v>6.47</v>
@@ -4146,7 +4925,7 @@
         <v>1.94</v>
       </c>
       <c r="N65" t="n">
-        <v>2.76</v>
+        <v>5.61</v>
       </c>
       <c r="O65" t="n">
         <v>-3.26</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="H66" t="n">
-        <v>1172.9</v>
+        <v>1167.7</v>
       </c>
       <c r="I66" t="n">
         <v>1168.660605483169</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K66" t="n">
-        <v>5.74</v>
+        <v>5.27</v>
       </c>
       <c r="L66" t="n">
         <v>4.32</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>7.26</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H67" t="n">
-        <v>1171</v>
+        <v>1226.1</v>
       </c>
       <c r="I67" t="n">
         <v>1213.168692417405</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.28</v>
+        <v>-5</v>
       </c>
       <c r="L67" t="n">
-        <v>4.39</v>
+        <v>6.82</v>
       </c>
       <c r="M67" t="n">
-        <v>3.42</v>
+        <v>5.04</v>
       </c>
       <c r="N67" t="n">
         <v>4.96</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H68" t="n">
-        <v>1435.9</v>
+        <v>1426.4</v>
       </c>
       <c r="I68" t="n">
         <v>1432.350829176892</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K68" t="n">
-        <v>17.11</v>
+        <v>16.34</v>
       </c>
       <c r="L68" t="n">
         <v>9.800000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.57</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="H69" t="n">
-        <v>1491.9</v>
+        <v>1534.2</v>
       </c>
       <c r="I69" t="n">
         <v>1509.815826183144</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.59</v>
+        <v>-7.56</v>
       </c>
       <c r="L69" t="n">
-        <v>5.93</v>
+        <v>8.15</v>
       </c>
       <c r="M69" t="n">
         <v>1.39</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.77</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H70" t="n">
-        <v>1621.4</v>
+        <v>1578.8</v>
       </c>
       <c r="I70" t="n">
         <v>1610.214598705139</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K70" t="n">
-        <v>5.68</v>
+        <v>2.91</v>
       </c>
       <c r="L70" t="n">
         <v>2.74</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>6</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.6</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.51</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.03</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.88</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>139.69</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.4</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.13</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.64</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.18</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="25">
@@ -9649,7 +10508,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.44</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.25</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
